--- a/Team-Data/2012-13/3-5-2012-13.xlsx
+++ b/Team-Data/2012-13/3-5-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -790,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -843,100 +910,100 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.542</v>
+        <v>0.534</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.346</v>
+        <v>0.341</v>
       </c>
       <c r="O3" t="n">
         <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
         <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="U3" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA3" t="n">
         <v>19.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -951,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
@@ -960,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -975,19 +1042,19 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1485,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1497,7 +1564,7 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -1673,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
@@ -1718,7 +1785,7 @@
         <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1876,7 +1943,7 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>15</v>
@@ -1885,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
         <v>15</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.645</v>
+        <v>0.639</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J9" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
         <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O9" t="n">
         <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.4</v>
@@ -1983,10 +2050,10 @@
         <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U9" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V9" t="n">
         <v>15.2</v>
@@ -2001,19 +2068,19 @@
         <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.7</v>
+        <v>105.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2040,7 +2107,7 @@
         <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2064,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2425,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2568,7 +2635,7 @@
         <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2592,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>6</v>
@@ -2601,7 +2668,7 @@
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>28</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2795,10 +2862,10 @@
         <v>26</v>
       </c>
       <c r="AV13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW13" t="n">
         <v>25</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2965,7 +3032,7 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -3027,67 +3094,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L15" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T15" t="n">
         <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
@@ -3096,16 +3163,16 @@
         <v>18.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
         <v>102.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3120,10 +3187,10 @@
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
@@ -3138,22 +3205,22 @@
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
         <v>16</v>
@@ -3162,10 +3229,10 @@
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3326,7 +3393,7 @@
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3347,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3499,7 +3566,7 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3705,7 +3772,7 @@
         <v>12</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K22" t="n">
         <v>0.483</v>
@@ -4331,7 +4398,7 @@
         <v>19.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="O22" t="n">
         <v>22.5</v>
@@ -4340,10 +4407,10 @@
         <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.832</v>
+        <v>0.831</v>
       </c>
       <c r="R22" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S22" t="n">
         <v>32.7</v>
@@ -4355,34 +4422,34 @@
         <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X22" t="n">
         <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
         <v>21.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>107</v>
+        <v>106.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,7 +4512,7 @@
         <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,46 +4750,46 @@
         <v>36.9</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L24" t="n">
         <v>6.2</v>
       </c>
       <c r="M24" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O24" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R24" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T24" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W24" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X24" t="n">
         <v>4.8</v>
@@ -4737,13 +4804,13 @@
         <v>16.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4758,7 +4825,7 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
@@ -4785,10 +4852,10 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4800,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4937,7 +5004,7 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
@@ -4991,7 +5058,7 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
         <v>18</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5235,22 +5302,22 @@
         <v>0.442</v>
       </c>
       <c r="L27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N27" t="n">
         <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
         <v>23.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
@@ -5262,49 +5329,49 @@
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V27" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
         <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
         <v>-6.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
         <v>7</v>
@@ -5313,7 +5380,7 @@
         <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM27" t="n">
         <v>16</v>
@@ -5346,10 +5413,10 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5358,10 +5425,10 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>9.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5850,7 +5917,7 @@
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
@@ -5901,13 +5968,13 @@
         <v>23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6059,7 +6126,7 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6083,7 +6150,7 @@
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-5-2012-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
     </row>
